--- a/results/link-prediction-gcn/Link/3shot/IMDB-BINARY/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/IMDB-BINARY/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4812±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5240±0.0044</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5186±0.0000</t>
+          <t>0.5292±0.0024</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5185±0.0004</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0004</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5185±0.0000</t>
+          <t>0.5579±0.0151</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5186±0.0005</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4812±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5286±0.0047</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5286±0.0075</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0004</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5186±0.0000</t>
+          <t>0.5562±0.0252</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4812±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5263±0.0027</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5186±0.0000</t>
+          <t>0.5260±0.0073</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5183±0.0005</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0005</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5183±0.0005</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5183±0.0005</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5183±0.0005</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5185±0.0004</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5579±0.0060</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.5783±0.0000</t>
+          <t>0.5486±0.0478</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5168±0.0016</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5181±0.0005</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5187±0.0000</t>
+          <t>0.5183±0.0005</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5094±0.0000</t>
+          <t>0.5113±0.0017</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5040±0.0000</t>
+          <t>0.5107±0.0005</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5069±0.0000</t>
+          <t>0.5178±0.0028</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5061±0.0000</t>
+          <t>0.5146±0.0040</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5061±0.0000</t>
+          <t>0.5146±0.0040</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5061±0.0000</t>
+          <t>0.5146±0.0040</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5174±0.0000</t>
+          <t>0.5214±0.0017</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5860±0.0000</t>
+          <t>0.5837±0.0297</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5183±0.0003</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4812±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5414±0.0000</t>
+          <t>0.5389±0.0256</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5190±0.0006</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5713±0.0000</t>
+          <t>0.5947±0.0051</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5159±0.0020</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4812±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5270±0.0044</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5249±0.0046</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5182±0.0007</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5180±0.0006</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0004</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5180±0.0008</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5180±0.0008</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5180±0.0008</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0004</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5360±0.0143</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5185±0.0004</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4853±0.0000</t>
+          <t>0.5140±0.0458</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.5193±0.0003</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5149±0.0029</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5182±0.0004</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.5184±0.0005</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5180±0.0009</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.5183±0.0004</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.5183±0.0004</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.5183±0.0004</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5136±0.0053</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6068±0.0000</t>
+          <t>0.5905±0.0028</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5185±0.0000</t>
+          <t>0.5187±0.0004</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6839±0.0004</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6829±0.0000</t>
+          <t>0.6854±0.0013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6881±0.0039</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6860±0.0025</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6849±0.0026</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.6829±0.0000</t>
+          <t>0.6877±0.0098</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,127 +1490,127 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6855±0.0020</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6830±0.0000</t>
+          <t>0.6851±0.0026</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6827±0.0004</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6827±0.0003</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6827±0.0004</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6827±0.0004</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6827±0.0004</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0004</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6879±0.0015</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.3534±0.0000</t>
+          <t>0.2493±0.1769</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6813±0.0014</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6820±0.0010</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6827±0.0004</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.6748±0.0000</t>
+          <t>0.6754±0.0024</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.6698±0.0000</t>
+          <t>0.6737±0.0005</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.6725±0.0000</t>
+          <t>0.6818±0.0021</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.6717±0.0000</t>
+          <t>0.6776±0.0041</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.6717±0.0000</t>
+          <t>0.6776±0.0041</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.6717±0.0000</t>
+          <t>0.6776±0.0041</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.6818±0.0000</t>
+          <t>0.6839±0.0008</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.7023±0.0000</t>
+          <t>0.7023±0.0103</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.6829±0.0000</t>
+          <t>0.6825±0.0002</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1620,62 +1620,62 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.6931±0.0000</t>
+          <t>0.6888±0.0069</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6827±0.0004</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.6864±0.0000</t>
+          <t>0.6989±0.0017</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6801±0.0021</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1685,127 +1685,127 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6856±0.0028</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6849±0.0016</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6826±0.0006</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6824±0.0005</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6824±0.0007</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6824±0.0007</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6824±0.0007</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6788±0.0047</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0154±0.0000</t>
+          <t>0.1175±0.1662</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6791±0.0030</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6826±0.0004</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.6827±0.0003</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6824±0.0008</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6826±0.0003</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6826±0.0003</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6826±0.0003</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6831±0.0000</t>
+          <t>0.6781±0.0053</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7154±0.0000</t>
+          <t>0.7110±0.0022</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6829±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.3352±0.0000</t>
+          <t>0.3351±0.0040</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7264±0.0028</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.7046±0.0000</t>
+          <t>0.7302±0.0079</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6939±0.0000</t>
+          <t>0.7141±0.0240</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7363±0.0025</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7219±0.0000</t>
+          <t>0.7291±0.0026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.7296±0.0025</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7326±0.0040</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7326±0.0040</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7326±0.0040</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.7313±0.0007</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.7346±0.0055</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7192±0.0000</t>
+          <t>0.7390±0.0053</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.3356±0.0000</t>
+          <t>0.3359±0.0037</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.7259±0.0035</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.6751±0.0000</t>
+          <t>0.7113±0.0038</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.7065±0.0000</t>
+          <t>0.6947±0.0187</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.7237±0.0000</t>
+          <t>0.7441±0.0030</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.7232±0.0000</t>
+          <t>0.7436±0.0038</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.7336±0.0046</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7230±0.0000</t>
+          <t>0.7447±0.0016</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7230±0.0000</t>
+          <t>0.7447±0.0016</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7230±0.0000</t>
+          <t>0.7447±0.0016</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.7312±0.0041</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7127±0.0000</t>
+          <t>0.7332±0.0057</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7199±0.0000</t>
+          <t>0.7458±0.0031</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.3356±0.0000</t>
+          <t>0.3356±0.0039</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7260±0.0034</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6773±0.0000</t>
+          <t>0.7286±0.0058</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7050±0.0000</t>
+          <t>0.7158±0.0236</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.7236±0.0000</t>
+          <t>0.7569±0.0039</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.7590±0.0021</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7293±0.0028</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7591±0.0027</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7591±0.0027</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7591±0.0027</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.7308±0.0014</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.6985±0.0000</t>
+          <t>0.7302±0.0029</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7193±0.0000</t>
+          <t>0.7670±0.0026</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6740±0.0000</t>
+          <t>0.6749±0.0025</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7326±0.0000</t>
+          <t>0.7334±0.0087</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.6880±0.0000</t>
+          <t>0.7298±0.0115</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.7085±0.0000</t>
+          <t>0.7327±0.0159</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.7120±0.0000</t>
+          <t>0.7275±0.0032</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.7104±0.0000</t>
+          <t>0.7328±0.0046</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.6967±0.0000</t>
+          <t>0.7299±0.0021</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.7120±0.0000</t>
+          <t>0.7303±0.0050</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.7120±0.0000</t>
+          <t>0.7303±0.0050</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.7120±0.0000</t>
+          <t>0.7303±0.0050</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.7207±0.0000</t>
+          <t>0.7184±0.0117</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7538±0.0000</t>
+          <t>0.7541±0.0032</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7208±0.0000</t>
+          <t>0.7412±0.0021</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.3357±0.0000</t>
+          <t>0.3358±0.0038</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.7222±0.0000</t>
+          <t>0.7252±0.0024</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.7691±0.0000</t>
+          <t>0.7708±0.0096</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.7125±0.0000</t>
+          <t>0.7485±0.0029</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.7219±0.0000</t>
+          <t>0.7258±0.0027</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.7222±0.0000</t>
+          <t>0.7255±0.0024</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.7224±0.0000</t>
+          <t>0.7256±0.0026</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7254±0.0025</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7254±0.0025</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7254±0.0025</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7259±0.0024</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7143±0.0000</t>
+          <t>0.7291±0.0045</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7175±0.0000</t>
+          <t>0.7258±0.0032</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.3356±0.0000</t>
+          <t>0.3358±0.0041</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7268±0.0025</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.7032±0.0000</t>
+          <t>0.7143±0.0152</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6975±0.0000</t>
+          <t>0.7394±0.0143</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.7224±0.0000</t>
+          <t>0.7359±0.0034</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7214±0.0000</t>
+          <t>0.7378±0.0044</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7282±0.0026</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7386±0.0049</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7386±0.0049</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7386±0.0049</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7320±0.0034</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6948±0.0000</t>
+          <t>0.7251±0.0052</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7194±0.0000</t>
+          <t>0.7443±0.0051</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.6985±0.0000</t>
+          <t>0.7168±0.0087</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7137±0.0000</t>
+          <t>0.7268±0.0023</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.6839±0.0000</t>
+          <t>0.7291±0.0219</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.7044±0.0000</t>
+          <t>0.7162±0.0149</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.7311±0.0000</t>
+          <t>0.7313±0.0096</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.7352±0.0000</t>
+          <t>0.7357±0.0026</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7081±0.0000</t>
+          <t>0.7336±0.0055</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7366±0.0000</t>
+          <t>0.7297±0.0021</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7366±0.0000</t>
+          <t>0.7297±0.0021</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7366±0.0000</t>
+          <t>0.7297±0.0021</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7151±0.0000</t>
+          <t>0.7304±0.0096</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7681±0.0000</t>
+          <t>0.7711±0.0025</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7502±0.0000</t>
+          <t>0.7605±0.0003</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4423±0.0000</t>
+          <t>0.4486±0.0030</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7442±0.0000</t>
+          <t>0.7466±0.0028</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.7131±0.0000</t>
+          <t>0.7489±0.0014</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7183±0.0000</t>
+          <t>0.7374±0.0161</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7457±0.0000</t>
+          <t>0.7536±0.0026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7453±0.0000</t>
+          <t>0.7485±0.0035</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7442±0.0000</t>
+          <t>0.7495±0.0029</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7511±0.0030</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7511±0.0030</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7511±0.0030</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.7494±0.0007</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7202±0.0000</t>
+          <t>0.7330±0.0068</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7374±0.0000</t>
+          <t>0.7497±0.0039</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4431±0.0000</t>
+          <t>0.4506±0.0023</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7442±0.0000</t>
+          <t>0.7425±0.0072</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6766±0.0000</t>
+          <t>0.7325±0.0083</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7301±0.0000</t>
+          <t>0.7253±0.0118</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7544±0.0036</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7536±0.0032</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7443±0.0000</t>
+          <t>0.7514±0.0027</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7471±0.0000</t>
+          <t>0.7532±0.0035</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7471±0.0000</t>
+          <t>0.7532±0.0035</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7471±0.0000</t>
+          <t>0.7532±0.0035</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7443±0.0000</t>
+          <t>0.7511±0.0045</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7126±0.0000</t>
+          <t>0.7306±0.0061</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7385±0.0000</t>
+          <t>0.7531±0.0017</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.4431±0.0000</t>
+          <t>0.4498±0.0028</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7442±0.0000</t>
+          <t>0.7487±0.0020</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6772±0.0000</t>
+          <t>0.7441±0.0114</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6967±0.0000</t>
+          <t>0.7399±0.0106</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7460±0.0000</t>
+          <t>0.7643±0.0029</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7468±0.0000</t>
+          <t>0.7638±0.0031</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7442±0.0000</t>
+          <t>0.7501±0.0028</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7468±0.0000</t>
+          <t>0.7659±0.0026</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7468±0.0000</t>
+          <t>0.7659±0.0026</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7468±0.0000</t>
+          <t>0.7659±0.0026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.7497±0.0018</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7041±0.0000</t>
+          <t>0.7262±0.0045</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7404±0.0000</t>
+          <t>0.7611±0.0033</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7182±0.0000</t>
+          <t>0.7171±0.0047</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7434±0.0000</t>
+          <t>0.7488±0.0050</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.6846±0.0000</t>
+          <t>0.7507±0.0074</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7337±0.0000</t>
+          <t>0.7513±0.0120</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.7413±0.0000</t>
+          <t>0.7549±0.0065</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7464±0.0000</t>
+          <t>0.7638±0.0027</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.7383±0.0000</t>
+          <t>0.7531±0.0016</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7482±0.0000</t>
+          <t>0.7584±0.0077</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7482±0.0000</t>
+          <t>0.7584±0.0077</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7482±0.0000</t>
+          <t>0.7584±0.0077</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.7447±0.0000</t>
+          <t>0.7486±0.0062</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7440±0.0043</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7419±0.0000</t>
+          <t>0.7531±0.0015</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.4432±0.0000</t>
+          <t>0.4502±0.0027</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7441±0.0000</t>
+          <t>0.7452±0.0043</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.7662±0.0000</t>
+          <t>0.7793±0.0024</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7377±0.0000</t>
+          <t>0.7613±0.0089</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7437±0.0000</t>
+          <t>0.7483±0.0032</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7446±0.0000</t>
+          <t>0.7476±0.0031</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7460±0.0000</t>
+          <t>0.7490±0.0024</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7477±0.0030</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7477±0.0030</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7477±0.0030</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7463±0.0000</t>
+          <t>0.7499±0.0040</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7297±0.0032</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7369±0.0000</t>
+          <t>0.7430±0.0034</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.4432±0.0000</t>
+          <t>0.4501±0.0032</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7442±0.0000</t>
+          <t>0.7415±0.0098</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.7028±0.0000</t>
+          <t>0.7373±0.0143</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6935±0.0000</t>
+          <t>0.7540±0.0135</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7439±0.0000</t>
+          <t>0.7524±0.0034</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7402±0.0000</t>
+          <t>0.7535±0.0030</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7441±0.0000</t>
+          <t>0.7502±0.0033</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7462±0.0000</t>
+          <t>0.7541±0.0021</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7462±0.0000</t>
+          <t>0.7541±0.0021</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7462±0.0000</t>
+          <t>0.7541±0.0021</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7441±0.0000</t>
+          <t>0.7497±0.0023</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7038±0.0000</t>
+          <t>0.7245±0.0043</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7391±0.0000</t>
+          <t>0.7514±0.0045</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7282±0.0000</t>
+          <t>0.7362±0.0018</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7473±0.0000</t>
+          <t>0.7451±0.0035</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.7469±0.0122</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.7257±0.0000</t>
+          <t>0.7352±0.0040</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7473±0.0000</t>
+          <t>0.7534±0.0066</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7522±0.0000</t>
+          <t>0.7591±0.0024</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7451±0.0000</t>
+          <t>0.7540±0.0034</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7519±0.0000</t>
+          <t>0.7558±0.0003</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7519±0.0000</t>
+          <t>0.7558±0.0003</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7519±0.0000</t>
+          <t>0.7558±0.0003</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7535±0.0000</t>
+          <t>0.7544±0.0059</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7545±0.0039</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7537±0.0000</t>
+          <t>0.7621±0.0014</t>
         </is>
       </c>
     </row>
